--- a/Sindhi Muslim/Student Attendance/home/Class 6 - Monthly Attendance - Aug to Nov.xlsx
+++ b/Sindhi Muslim/Student Attendance/home/Class 6 - Monthly Attendance - Aug to Nov.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24E1A9F-9855-4FBF-9217-AB8CE5DD16E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ADFC888-B42B-48FD-A8D9-26548E91F572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="626" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4418" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4463" uniqueCount="122">
   <si>
     <t>S.No</t>
   </si>
@@ -4689,11 +4689,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="Q5:Q47"/>
-    <mergeCell ref="U5:U47"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="Y8:AB8"/>
-    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="I5:I47"/>
+    <mergeCell ref="P5:P47"/>
+    <mergeCell ref="K5:K47"/>
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="A2:X2"/>
     <mergeCell ref="A3:A4"/>
@@ -4703,9 +4701,11 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
-    <mergeCell ref="I5:I47"/>
-    <mergeCell ref="P5:P47"/>
-    <mergeCell ref="K5:K47"/>
+    <mergeCell ref="Q5:Q47"/>
+    <mergeCell ref="U5:U47"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="Y8:AB8"/>
+    <mergeCell ref="Y16:AB16"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B35">
     <cfRule type="duplicateValues" dxfId="51" priority="13"/>
@@ -9854,6 +9854,9 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL16:AO16"/>
     <mergeCell ref="F5:F49"/>
     <mergeCell ref="M5:M49"/>
     <mergeCell ref="T5:T49"/>
@@ -9870,9 +9873,6 @@
     <mergeCell ref="AH5:AH49"/>
     <mergeCell ref="K5:K49"/>
     <mergeCell ref="V5:V49"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL16:AO16"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B37">
     <cfRule type="duplicateValues" dxfId="38" priority="1"/>
@@ -15130,6 +15130,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="Y5:Y47"/>
     <mergeCell ref="AF5:AF47"/>
     <mergeCell ref="Q5:Q47"/>
     <mergeCell ref="A2:AL2"/>
@@ -15146,7 +15147,6 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="K5:K47"/>
     <mergeCell ref="R5:R47"/>
-    <mergeCell ref="Y5:Y47"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B35">
     <cfRule type="duplicateValues" dxfId="25" priority="1"/>
@@ -15644,7 +15644,7 @@
         <v>23</v>
       </c>
       <c r="T5" s="23" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="U5" s="23" t="s">
         <v>23</v>
@@ -15662,7 +15662,7 @@
         <v>23</v>
       </c>
       <c r="Z5" s="23" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="AA5" s="23" t="s">
         <v>23</v>
@@ -15688,14 +15688,16 @@
       <c r="AH5" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI5" s="23"/>
+      <c r="AI5" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ5" s="5">
         <f t="shared" ref="AJ5:AJ49" si="1">COUNTIF(F5:AI5,"P")</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK5" s="5">
         <f t="shared" ref="AK5:AK49" si="2">COUNTIF(F5:AI5,"A")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL5" s="5" t="s">
         <v>8</v>
@@ -15801,10 +15803,12 @@
       <c r="AH6" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI6" s="23"/>
+      <c r="AI6" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ6" s="5">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" si="2"/>
@@ -15836,10 +15840,10 @@
         <v>24</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="H7" s="41"/>
       <c r="I7" s="23" t="s">
@@ -15860,10 +15864,10 @@
       <c r="N7" s="30"/>
       <c r="O7" s="41"/>
       <c r="P7" s="23" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="Q7" s="23" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="R7" s="23" t="s">
         <v>70</v>
@@ -15872,10 +15876,10 @@
         <v>23</v>
       </c>
       <c r="T7" s="23" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="U7" s="23" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="V7" s="41"/>
       <c r="W7" s="23" t="s">
@@ -15888,7 +15892,7 @@
         <v>23</v>
       </c>
       <c r="Z7" s="23" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="AA7" s="23" t="s">
         <v>23</v>
@@ -15912,14 +15916,16 @@
       <c r="AH7" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI7" s="23"/>
+      <c r="AI7" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ7" s="5">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AK7" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
@@ -16019,10 +16025,12 @@
       <c r="AH8" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI8" s="23"/>
+      <c r="AI8" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ8" s="5">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK8" s="5">
         <f t="shared" si="2"/>
@@ -16128,10 +16136,12 @@
       <c r="AH9" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI9" s="23"/>
+      <c r="AI9" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ9" s="5">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK9" s="5">
         <f t="shared" si="2"/>
@@ -16243,10 +16253,12 @@
       <c r="AH10" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI10" s="23"/>
+      <c r="AI10" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ10" s="5">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK10" s="5">
         <f t="shared" si="2"/>
@@ -16361,10 +16373,12 @@
       <c r="AH11" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI11" s="23"/>
+      <c r="AI11" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ11" s="5">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" si="2"/>
@@ -16375,15 +16389,15 @@
       </c>
       <c r="AM11" s="8">
         <f>AJ31+AJ32+AJ35++AJ44</f>
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AN11" s="8">
         <f>AJ30+AJ33+AJ34+AJ36+AJ37+AJ38+AJ39+AJ40+AJ41+AJ42+AJ43+AJ45+AJ46</f>
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="AO11" s="8">
         <f>AM11+AN11</f>
-        <v>380</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
@@ -16479,10 +16493,12 @@
       <c r="AH12" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI12" s="23"/>
+      <c r="AI12" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ12" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="2"/>
@@ -16493,15 +16509,15 @@
       </c>
       <c r="AM12" s="8">
         <f>AM11/AM10</f>
-        <v>0.18421052631578946</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="AN12" s="8">
         <f>AN11/AN10</f>
-        <v>0.52930402930402931</v>
+        <v>0.55311355311355315</v>
       </c>
       <c r="AO12" s="8">
         <f>AO11/AO10</f>
-        <v>0.36538461538461536</v>
+        <v>0.38173076923076921</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
@@ -16597,10 +16613,12 @@
       <c r="AH13" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI13" s="23"/>
+      <c r="AI13" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ13" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="2"/>
@@ -16704,10 +16722,12 @@
       <c r="AH14" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AI14" s="23"/>
+      <c r="AI14" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ14" s="5">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="2"/>
@@ -16811,10 +16831,12 @@
       <c r="AH15" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AI15" s="23"/>
+      <c r="AI15" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ15" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="2"/>
@@ -16918,10 +16940,12 @@
       <c r="AH16" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AI16" s="23"/>
+      <c r="AI16" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ16" s="5">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="2"/>
@@ -17027,10 +17051,12 @@
       <c r="AH17" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AI17" s="23"/>
+      <c r="AI17" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ17" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="2"/>
@@ -17142,10 +17168,12 @@
       <c r="AH18" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AI18" s="23"/>
+      <c r="AI18" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ18" s="5">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="2"/>
@@ -17260,10 +17288,12 @@
       <c r="AH19" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AI19" s="23"/>
+      <c r="AI19" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ19" s="5">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="2"/>
@@ -17274,15 +17304,15 @@
       </c>
       <c r="AM19" s="8">
         <f>AM18-AM11</f>
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AN19" s="8">
         <f>AN18-AN11</f>
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="AO19" s="8">
         <f>AM19+AN19</f>
-        <v>660</v>
+        <v>643</v>
       </c>
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
@@ -17378,10 +17408,12 @@
       <c r="AH20" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AI20" s="23"/>
+      <c r="AI20" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ20" s="5">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="2"/>
@@ -17392,15 +17424,15 @@
       </c>
       <c r="AM20" s="13">
         <f>AM19/AM18</f>
-        <v>0.81578947368421051</v>
+        <v>0.80769230769230771</v>
       </c>
       <c r="AN20" s="13">
         <f>AN19/AN18</f>
-        <v>0.47069597069597069</v>
+        <v>0.44688644688644691</v>
       </c>
       <c r="AO20" s="13">
         <f>AO19/AO18</f>
-        <v>0.63461538461538458</v>
+        <v>0.61826923076923079</v>
       </c>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
@@ -17494,10 +17526,12 @@
       <c r="AH21" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AI21" s="23"/>
+      <c r="AI21" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ21" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="2"/>
@@ -17597,10 +17631,12 @@
       <c r="AH22" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI22" s="23"/>
+      <c r="AI22" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ22" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="2"/>
@@ -17700,10 +17736,12 @@
       <c r="AH23" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI23" s="23"/>
+      <c r="AI23" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ23" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="2"/>
@@ -17803,10 +17841,12 @@
       <c r="AH24" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI24" s="23"/>
+      <c r="AI24" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ24" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="2"/>
@@ -17906,10 +17946,12 @@
       <c r="AH25" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI25" s="23"/>
+      <c r="AI25" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ25" s="5">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="2"/>
@@ -18009,10 +18051,12 @@
       <c r="AH26" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI26" s="23"/>
+      <c r="AI26" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ26" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="2"/>
@@ -18112,10 +18156,12 @@
       <c r="AH27" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI27" s="23"/>
+      <c r="AI27" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ27" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="2"/>
@@ -18215,10 +18261,12 @@
       <c r="AH28" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI28" s="23"/>
+      <c r="AI28" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ28" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="2"/>
@@ -18318,10 +18366,12 @@
       <c r="AH29" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI29" s="23"/>
+      <c r="AI29" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ29" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="2"/>
@@ -18421,10 +18471,12 @@
       <c r="AH30" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI30" s="23"/>
+      <c r="AI30" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ30" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="2"/>
@@ -18524,10 +18576,12 @@
       <c r="AH31" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI31" s="23"/>
+      <c r="AI31" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ31" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="2"/>
@@ -18627,10 +18681,12 @@
       <c r="AH32" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI32" s="23"/>
+      <c r="AI32" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ32" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="2"/>
@@ -18730,10 +18786,12 @@
       <c r="AH33" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI33" s="23"/>
+      <c r="AI33" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ33" s="5">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK33" s="5">
         <f t="shared" si="2"/>
@@ -18833,10 +18891,12 @@
       <c r="AH34" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI34" s="23"/>
+      <c r="AI34" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ34" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK34" s="5">
         <f t="shared" si="2"/>
@@ -18936,10 +18996,12 @@
       <c r="AH35" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI35" s="23"/>
+      <c r="AI35" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ35" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK35" s="5">
         <f t="shared" si="2"/>
@@ -19039,10 +19101,12 @@
       <c r="AH36" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI36" s="23"/>
+      <c r="AI36" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ36" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="2"/>
@@ -19142,10 +19206,12 @@
       <c r="AH37" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI37" s="23"/>
+      <c r="AI37" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ37" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="2"/>
@@ -19245,10 +19311,12 @@
       <c r="AH38" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI38" s="23"/>
+      <c r="AI38" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ38" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK38" s="5">
         <f t="shared" si="2"/>
@@ -19348,10 +19416,12 @@
       <c r="AH39" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI39" s="23"/>
+      <c r="AI39" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ39" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK39" s="5">
         <f t="shared" si="2"/>
@@ -19451,10 +19521,12 @@
       <c r="AH40" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI40" s="23"/>
+      <c r="AI40" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ40" s="5">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="2"/>
@@ -19554,10 +19626,12 @@
       <c r="AH41" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI41" s="23"/>
+      <c r="AI41" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ41" s="5">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="2"/>
@@ -19657,10 +19731,12 @@
       <c r="AH42" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI42" s="23"/>
+      <c r="AI42" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ42" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK42" s="5">
         <f t="shared" si="2"/>
@@ -19760,10 +19836,12 @@
       <c r="AH43" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI43" s="23"/>
+      <c r="AI43" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ43" s="5">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK43" s="5">
         <f t="shared" si="2"/>
@@ -19863,10 +19941,12 @@
       <c r="AH44" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI44" s="23"/>
+      <c r="AI44" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ44" s="5">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="2"/>
@@ -19966,10 +20046,12 @@
       <c r="AH45" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI45" s="23"/>
+      <c r="AI45" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ45" s="5">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="2"/>
@@ -20069,10 +20151,12 @@
       <c r="AH46" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI46" s="23"/>
+      <c r="AI46" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ46" s="5">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK46" s="5">
         <f t="shared" si="2"/>
@@ -20170,10 +20254,12 @@
       <c r="AH47" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI47" s="23"/>
+      <c r="AI47" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ47" s="5">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK47" s="5">
         <f t="shared" si="2"/>
@@ -20271,10 +20357,12 @@
       <c r="AH48" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI48" s="23"/>
+      <c r="AI48" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ48" s="5">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK48" s="5">
         <f t="shared" si="2"/>
@@ -20371,10 +20459,12 @@
       <c r="AH49" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AI49" s="23"/>
+      <c r="AI49" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ49" s="5">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK49" s="5">
         <f t="shared" si="2"/>
@@ -20383,11 +20473,9 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AC5:AC49"/>
-    <mergeCell ref="N5:N49"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="H5:H49"/>
+    <mergeCell ref="O5:O49"/>
+    <mergeCell ref="V5:V49"/>
     <mergeCell ref="A1:AK1"/>
     <mergeCell ref="A2:AK2"/>
     <mergeCell ref="A3:A4"/>
@@ -20397,19 +20485,21 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="H5:H49"/>
-    <mergeCell ref="O5:O49"/>
-    <mergeCell ref="V5:V49"/>
+    <mergeCell ref="AC5:AC49"/>
+    <mergeCell ref="N5:N49"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL16:AO16"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B35">
     <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:O5 V5 AC5 P5:U49 W5:AB49 AD5:AI49 F6:G49 I6:M49 F4:AI4">
+  <conditionalFormatting sqref="F5:O5 V5 AC5 P5:U49 W5:AB49 F6:G49 I6:M49 F4:AI4 AD5:AI49">
     <cfRule type="expression" dxfId="11" priority="11">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:O5 V5 AC5 P5:U49 W5:AB49 AD5:AI49 F6:G49 I6:M49">
+  <conditionalFormatting sqref="F5:O5 V5 AC5 P5:U49 W5:AB49 F6:G49 I6:M49 AD5:AI49">
     <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
       <formula>"L"</formula>
     </cfRule>
@@ -20420,7 +20510,7 @@
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:AI4 F5:O5 V5 AC5 P5:U49 W5:AB49 AD5:AI49 F6:G49 I6:M49">
+  <conditionalFormatting sqref="F3:AI4 F5:O5 V5 AC5 P5:U49 W5:AB49 F6:G49 I6:M49 AD5:AI49">
     <cfRule type="expression" dxfId="7" priority="12">
       <formula>F$3="Sun"</formula>
     </cfRule>
